--- a/rb2.xlsx
+++ b/rb2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdash\Downloads\Excel clean\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdash\Downloads\Excel-clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95D3A82-629C-4E4A-BBCA-BD57F877621B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7CC30E-5A23-4AC7-B56C-0AB022682403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C2F2230-33F4-424C-BED6-B0E404033255}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="38">
   <si>
     <t>Project:</t>
   </si>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>Deducts D=1/2</t>
+  </si>
+  <si>
+    <t>DR</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1169,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
